--- a/data/admissions_registry.xlsx
+++ b/data/admissions_registry.xlsx
@@ -1,15 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5340" yWindow="2316" windowWidth="17280" windowHeight="9420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$V$2</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -45,11 +48,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,12 +416,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="35" customWidth="1" min="17" max="17"/>
+    <col width="53" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Telegram ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ссылка Telegram</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ФИО</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Телефон</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Бірлестік / кафедра</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Специальность</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Курс</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Аттестат/диплом</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Удостоверение личности</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Фото 3x4</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Справка 075/у</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Сертификат ЕНТ</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Бірлестік / кафедра (поступление)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Специальность поступления</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Расчетная скидка</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Расчетная цена за год</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Расчетная цена за 4 года</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Статус проверки</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="n">
         <v>5394280567</v>
@@ -434,7 +571,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4t4t4t4</t>
+          <t>grgrgrg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -444,61 +581,88 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Студент</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Инженерные технологии</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ВТПО 23-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAICB2nvdtnjYNB5QPwYLkaqEiBJNhT5AAKVFWsbNoR5S-3IVjlCqZNiAQADAgADeAADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAICB2nvdtnjYNB5QPwYLkaqEiBJNhT5AAKVFWsbNoR5S-3IVjlCqZNiAQADAgADeAADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAICB2nvdtnjYNB5QPwYLkaqEiBJNhT5AAKVFWsbNoR5S-3IVjlCqZNiAQADAgADeAADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAICB2nvdtnjYNB5QPwYLkaqEiBJNhT5AAKVFWsbNoR5S-3IVjlCqZNiAQADAgADeAADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAICB2nvdtnjYNB5QPwYLkaqEiBJNhT5AAKVFWsbNoR5S-3IVjlCqZNiAQADAgADeAADOwQ; server_path: data/files/5394280567/ent_certificate.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIJ6WoKH4mHrHW6Md7lvGUkJl6HKDptAAL7HmsbN2ZQSLPiMeUW-uXHAQADAgADeQADOwQ; server_path: data/files/5394280567/ent_certificate.jpg</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>efef</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Педагогика</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>6В01301 - Педагогика и методика начального обучения</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>450000</v>
+      </c>
+      <c r="U2" s="1" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>